--- a/JsonConverter/ExcelFiles/SpawnZoneData.xlsx
+++ b/JsonConverter/ExcelFiles/SpawnZoneData.xlsx
@@ -20,27 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
   <si>
-    <t xml:space="preserve">타겟 이름</t>
-  </si>
-  <si>
-    <t xml:space="preserve">타겟 사이즈</t>
-  </si>
-  <si>
-    <t xml:space="preserve">타겟 점수</t>
-  </si>
-  <si>
-    <t xml:space="preserve">타겟 크기</t>
-  </si>
-  <si>
-    <t xml:space="preserve">타겟 프리팹 키</t>
-  </si>
-  <si>
-    <t xml:space="preserve">타겟 티어</t>
+    <t xml:space="preserve">맵 이름</t>
+  </si>
+  <si>
+    <t xml:space="preserve">맵 타입</t>
   </si>
   <si>
     <t xml:space="preserve">string</t>
@@ -55,16 +43,22 @@
     <t xml:space="preserve">ZoneName</t>
   </si>
   <si>
-    <t xml:space="preserve">CenterX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CenterZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InnerRadius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OuterRadius</t>
+    <t xml:space="preserve">ZoneType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MinX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MinZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PlacementType</t>
   </si>
   <si>
     <t xml:space="preserve">Target_List</t>
@@ -79,34 +73,58 @@
     <t xml:space="preserve">공원</t>
   </si>
   <si>
-    <t xml:space="preserve">Target_01,Target_02,Target_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60,30,25</t>
+    <t xml:space="preserve">Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scatter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target_01,Target_02,Target_03,Target_04,Target_05,Target_06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55,32,20,7,3,1</t>
   </si>
   <si>
     <t xml:space="preserve">Zone_02</t>
   </si>
   <si>
-    <t xml:space="preserve">도로</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target_03,Target_04,Target_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30,35,15</t>
+    <t xml:space="preserve">빌라촌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22,14,18,24,11,16</t>
   </si>
   <si>
     <t xml:space="preserve">Zone_03</t>
   </si>
   <si>
-    <t xml:space="preserve">주택가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target_04,Target_05,Target_06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20,20,12</t>
+    <t xml:space="preserve">시내</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downtown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38,10,24,32,16,6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zone_04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">군부대</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Military</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,8,18,26,20</t>
   </si>
 </sst>
 </file>
@@ -296,7 +314,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -565,20 +583,20 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S1000"/>
+  <dimension ref="A1:U1000"/>
   <sheetFormatPr defaultColWidth="11.53125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="26.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="44.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="24.37"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="11" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="18.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="24.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="26.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="16.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="44.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="24.37"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="13" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" s="3" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -591,103 +609,111 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
     </row>
     <row r="2" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
     </row>
     <row r="3" s="7" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="5"/>
+      <c r="K3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="D4" s="10" t="n">
+        <v>-140</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>140</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>-320</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>-100</v>
+      </c>
+      <c r="H4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="9" t="n">
+      <c r="I4" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="10" t="n">
-        <v>120</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="9"/>
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="12"/>
@@ -695,6 +721,8 @@
       <c r="Q4" s="12"/>
       <c r="R4" s="12"/>
       <c r="S4" s="12"/>
+      <c r="T4" s="12"/>
+      <c r="U4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
@@ -703,27 +731,31 @@
       <c r="B5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="10" t="n">
-        <v>0</v>
+      <c r="C5" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="9" t="n">
+        <v>-140</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>140</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G5" s="10" t="n">
         <v>120</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>260</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="H5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
+      <c r="I5" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="11"/>
       <c r="L5" s="12"/>
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
@@ -732,35 +764,41 @@
       <c r="Q5" s="12"/>
       <c r="R5" s="12"/>
       <c r="S5" s="12"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="10" t="n">
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>260</v>
+        <v>-140</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>140</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>420</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>27</v>
+        <v>120</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>340</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" s="9"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="9"/>
       <c r="L6" s="12"/>
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
@@ -769,19 +807,41 @@
       <c r="Q6" s="12"/>
       <c r="R6" s="12"/>
       <c r="S6" s="12"/>
+      <c r="T6" s="12"/>
+      <c r="U6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
+      <c r="A7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>-140</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>140</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>340</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>560</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="9"/>
       <c r="L7" s="12"/>
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
@@ -790,6 +850,8 @@
       <c r="Q7" s="12"/>
       <c r="R7" s="12"/>
       <c r="S7" s="12"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8"/>
@@ -797,12 +859,12 @@
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
-      <c r="F8" s="10"/>
+      <c r="F8" s="9"/>
       <c r="G8" s="10"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
       <c r="L8" s="12"/>
       <c r="M8" s="12"/>
       <c r="N8" s="12"/>
@@ -811,6 +873,8 @@
       <c r="Q8" s="12"/>
       <c r="R8" s="12"/>
       <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+      <c r="U8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8"/>
@@ -818,12 +882,12 @@
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
-      <c r="F9" s="10"/>
+      <c r="F9" s="9"/>
       <c r="G9" s="10"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
       <c r="L9" s="12"/>
       <c r="M9" s="12"/>
       <c r="N9" s="12"/>
@@ -832,6 +896,8 @@
       <c r="Q9" s="12"/>
       <c r="R9" s="12"/>
       <c r="S9" s="12"/>
+      <c r="T9" s="12"/>
+      <c r="U9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9"/>
@@ -843,8 +909,8 @@
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
       <c r="L10" s="12"/>
       <c r="M10" s="12"/>
       <c r="N10" s="12"/>
@@ -853,6 +919,8 @@
       <c r="Q10" s="12"/>
       <c r="R10" s="12"/>
       <c r="S10" s="12"/>
+      <c r="T10" s="12"/>
+      <c r="U10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9"/>
@@ -864,8 +932,8 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
       <c r="L11" s="12"/>
       <c r="M11" s="12"/>
       <c r="N11" s="12"/>
@@ -874,6 +942,8 @@
       <c r="Q11" s="12"/>
       <c r="R11" s="12"/>
       <c r="S11" s="12"/>
+      <c r="T11" s="12"/>
+      <c r="U11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9"/>
@@ -885,8 +955,8 @@
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
       <c r="L12" s="12"/>
       <c r="M12" s="12"/>
       <c r="N12" s="12"/>
@@ -895,6 +965,8 @@
       <c r="Q12" s="12"/>
       <c r="R12" s="12"/>
       <c r="S12" s="12"/>
+      <c r="T12" s="12"/>
+      <c r="U12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9"/>
@@ -906,8 +978,8 @@
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
       <c r="L13" s="12"/>
       <c r="M13" s="12"/>
       <c r="N13" s="12"/>
@@ -916,6 +988,8 @@
       <c r="Q13" s="12"/>
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
+      <c r="T13" s="12"/>
+      <c r="U13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9"/>
@@ -927,8 +1001,8 @@
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
       <c r="L14" s="12"/>
       <c r="M14" s="12"/>
       <c r="N14" s="12"/>
@@ -937,6 +1011,8 @@
       <c r="Q14" s="12"/>
       <c r="R14" s="12"/>
       <c r="S14" s="12"/>
+      <c r="T14" s="12"/>
+      <c r="U14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9"/>
@@ -948,8 +1024,8 @@
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
       <c r="L15" s="12"/>
       <c r="M15" s="12"/>
       <c r="N15" s="12"/>
@@ -958,6 +1034,8 @@
       <c r="Q15" s="12"/>
       <c r="R15" s="12"/>
       <c r="S15" s="12"/>
+      <c r="T15" s="12"/>
+      <c r="U15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12"/>
@@ -969,6 +1047,8 @@
       <c r="G16" s="12"/>
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="12"/>
@@ -980,6 +1060,8 @@
       <c r="G17" s="12"/>
       <c r="H17" s="12"/>
       <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12"/>
@@ -991,6 +1073,8 @@
       <c r="G18" s="12"/>
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12"/>
@@ -1002,6 +1086,8 @@
       <c r="G19" s="12"/>
       <c r="H19" s="12"/>
       <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12"/>
@@ -1013,6 +1099,8 @@
       <c r="G20" s="12"/>
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12"/>
@@ -1024,6 +1112,8 @@
       <c r="G21" s="12"/>
       <c r="H21" s="12"/>
       <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12"/>
@@ -1035,6 +1125,8 @@
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
       <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12"/>
@@ -1046,6 +1138,8 @@
       <c r="G23" s="12"/>
       <c r="H23" s="12"/>
       <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12"/>
@@ -1057,6 +1151,8 @@
       <c r="G24" s="12"/>
       <c r="H24" s="12"/>
       <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12"/>
@@ -1068,6 +1164,8 @@
       <c r="G25" s="12"/>
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12"/>
@@ -1079,6 +1177,8 @@
       <c r="G26" s="12"/>
       <c r="H26" s="12"/>
       <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="12"/>
@@ -1090,6 +1190,8 @@
       <c r="G27" s="12"/>
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12"/>
@@ -1101,6 +1203,8 @@
       <c r="G28" s="12"/>
       <c r="H28" s="12"/>
       <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="12"/>
@@ -1112,6 +1216,8 @@
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="12"/>
@@ -1123,6 +1229,8 @@
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="12"/>
@@ -1134,6 +1242,8 @@
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="12"/>
@@ -1145,6 +1255,8 @@
       <c r="G32" s="12"/>
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="12"/>
@@ -1156,6 +1268,8 @@
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="12"/>
@@ -1167,6 +1281,8 @@
       <c r="G34" s="12"/>
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="12"/>
@@ -1178,6 +1294,8 @@
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/JsonConverter/ExcelFiles/SpawnZoneData.xlsx
+++ b/JsonConverter/ExcelFiles/SpawnZoneData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -637,14 +637,18 @@
       <c r="F2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="2"/>
+      <c r="J2" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
